--- a/docs/design-vi/ACSMS-SCR-013/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者履歴情報画面_v1.0.xlsx
+++ b/docs/design-vi/ACSMS-SCR-013/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者履歴情報画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1361,20 +1361,80 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>Bổ sung 7 ca kiểm thử cho API hủy lịch sử (ACSMS-API-013-002): điều kiện kích hoạt nút "取消", luồng hủy thành công (thêm dòng đỏ + tính lại master), kiểm tra lý do hủy, gọi API trực tiếp vào dòng không được hủy, DataScope/quyền sở hữu của dòng lịch sử, hiển thị dòng đã hủy, và nội dung cột người tạo (created_by)</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6346,7 +6406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ49"/>
+  <dimension ref="A1:BQ57"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -14648,17 +14708,737 @@
       <c r="BP49" s="10" t="n"/>
       <c r="BQ49" s="11" t="n"/>
     </row>
+    <row r="50" ht="22.5" customHeight="1">
+      <c r="A50" s="32" t="inlineStr">
+        <is>
+          <t>Hủy lịch sử・Hiển thị người tạo (Function — Torikeshi / Created-by)</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="10" t="n"/>
+      <c r="J50" s="10" t="n"/>
+      <c r="K50" s="10" t="n"/>
+      <c r="L50" s="10" t="n"/>
+      <c r="M50" s="10" t="n"/>
+      <c r="N50" s="10" t="n"/>
+      <c r="O50" s="10" t="n"/>
+      <c r="P50" s="10" t="n"/>
+      <c r="Q50" s="10" t="n"/>
+      <c r="R50" s="10" t="n"/>
+      <c r="S50" s="10" t="n"/>
+      <c r="T50" s="10" t="n"/>
+      <c r="U50" s="10" t="n"/>
+      <c r="V50" s="10" t="n"/>
+      <c r="W50" s="10" t="n"/>
+      <c r="X50" s="10" t="n"/>
+      <c r="Y50" s="10" t="n"/>
+      <c r="Z50" s="10" t="n"/>
+      <c r="AA50" s="10" t="n"/>
+      <c r="AB50" s="10" t="n"/>
+      <c r="AC50" s="10" t="n"/>
+      <c r="AD50" s="10" t="n"/>
+      <c r="AE50" s="10" t="n"/>
+      <c r="AF50" s="10" t="n"/>
+      <c r="AG50" s="10" t="n"/>
+      <c r="AH50" s="10" t="n"/>
+      <c r="AI50" s="10" t="n"/>
+      <c r="AJ50" s="10" t="n"/>
+      <c r="AK50" s="10" t="n"/>
+      <c r="AL50" s="10" t="n"/>
+      <c r="AM50" s="10" t="n"/>
+      <c r="AN50" s="10" t="n"/>
+      <c r="AO50" s="10" t="n"/>
+      <c r="AP50" s="10" t="n"/>
+      <c r="AQ50" s="10" t="n"/>
+      <c r="AR50" s="10" t="n"/>
+      <c r="AS50" s="10" t="n"/>
+      <c r="AT50" s="10" t="n"/>
+      <c r="AU50" s="10" t="n"/>
+      <c r="AV50" s="10" t="n"/>
+      <c r="AW50" s="10" t="n"/>
+      <c r="AX50" s="10" t="n"/>
+      <c r="AY50" s="10" t="n"/>
+      <c r="AZ50" s="10" t="n"/>
+      <c r="BA50" s="10" t="n"/>
+      <c r="BB50" s="10" t="n"/>
+      <c r="BC50" s="10" t="n"/>
+      <c r="BD50" s="10" t="n"/>
+      <c r="BE50" s="10" t="n"/>
+      <c r="BF50" s="10" t="n"/>
+      <c r="BG50" s="10" t="n"/>
+      <c r="BH50" s="10" t="n"/>
+      <c r="BI50" s="10" t="n"/>
+      <c r="BJ50" s="10" t="n"/>
+      <c r="BK50" s="10" t="n"/>
+      <c r="BL50" s="10" t="n"/>
+      <c r="BM50" s="10" t="n"/>
+      <c r="BN50" s="10" t="n"/>
+      <c r="BO50" s="10" t="n"/>
+      <c r="BP50" s="10" t="n"/>
+      <c r="BQ50" s="11" t="n"/>
+    </row>
+    <row r="51" ht="384" customHeight="1">
+      <c r="A51" s="44" t="n">
+        <v>34</v>
+      </c>
+      <c r="B51" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-013-034</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="11" t="n"/>
+      <c r="E51" s="46" t="inlineStr">
+        <is>
+          <t>Logic nghiệp vụ — Điều kiện kích hoạt nút "取消" (yêu cầu khách hàng 2026-07)</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="11" t="n"/>
+      <c r="J51" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (thuộc ja_id=100, có quyền `dokusya.update`)
+・Người đọc bản giấy (dokusya_shubetsu=1) có các dòng lịch sử sau:
+・(a) Dòng đăng ký mới (rireki_no=1, shinki_flg=true)
+・(b) Dòng cuối chuỗi có ngày áp dụng ở tương lai (thay đổi thông thường: tăng số bản, đổi địa chỉ...)
+・(c) Dòng trung gian nằm trước (b) (phía sau còn dòng chưa hủy)
+・(d) Dòng có ngày áp dụng đã đến (ngày áp dụng ≤ hôm nay, JST)
+・(e) Dòng đã hủy (torikeshi_flg=true)
+・Tồn tại mỗi loại 1 người đọc bản điện tử (dokusya_shubetsu=2) và người đọc kết hợp (3)</t>
+        </is>
+      </c>
+      <c r="K51" s="10" t="n"/>
+      <c r="L51" s="10" t="n"/>
+      <c r="M51" s="10" t="n"/>
+      <c r="N51" s="10" t="n"/>
+      <c r="O51" s="10" t="n"/>
+      <c r="P51" s="11" t="n"/>
+      <c r="Q51" s="46" t="inlineStr"/>
+      <c r="R51" s="10" t="n"/>
+      <c r="S51" s="10" t="n"/>
+      <c r="T51" s="10" t="n"/>
+      <c r="U51" s="10" t="n"/>
+      <c r="V51" s="10" t="n"/>
+      <c r="W51" s="11" t="n"/>
+      <c r="X51" s="46" t="inlineStr"/>
+      <c r="Y51" s="10" t="n"/>
+      <c r="Z51" s="10" t="n"/>
+      <c r="AA51" s="10" t="n"/>
+      <c r="AB51" s="10" t="n"/>
+      <c r="AC51" s="10" t="n"/>
+      <c r="AD51" s="11" t="n"/>
+      <c r="AE51" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF51" s="11" t="n"/>
+      <c r="AG51" s="45" t="inlineStr"/>
+      <c r="AH51" s="10" t="n"/>
+      <c r="AI51" s="11" t="n"/>
+      <c r="AJ51" s="45" t="inlineStr"/>
+      <c r="AK51" s="10" t="n"/>
+      <c r="AL51" s="11" t="n"/>
+      <c r="AM51" s="45" t="inlineStr"/>
+      <c r="AN51" s="10" t="n"/>
+      <c r="AO51" s="11" t="n"/>
+      <c r="AP51" s="45" t="inlineStr"/>
+      <c r="AQ51" s="10" t="n"/>
+      <c r="AR51" s="11" t="n"/>
+      <c r="AS51" s="45" t="inlineStr"/>
+      <c r="AT51" s="10" t="n"/>
+      <c r="AU51" s="11" t="n"/>
+      <c r="AV51" s="45" t="inlineStr"/>
+      <c r="AW51" s="10" t="n"/>
+      <c r="AX51" s="11" t="n"/>
+      <c r="AY51" s="45" t="inlineStr"/>
+      <c r="AZ51" s="10" t="n"/>
+      <c r="BA51" s="11" t="n"/>
+      <c r="BB51" s="45" t="inlineStr"/>
+      <c r="BC51" s="10" t="n"/>
+      <c r="BD51" s="11" t="n"/>
+      <c r="BE51" s="45" t="inlineStr"/>
+      <c r="BF51" s="10" t="n"/>
+      <c r="BG51" s="11" t="n"/>
+      <c r="BH51" s="45" t="inlineStr"/>
+      <c r="BI51" s="10" t="n"/>
+      <c r="BJ51" s="11" t="n"/>
+      <c r="BK51" s="46" t="inlineStr"/>
+      <c r="BL51" s="10" t="n"/>
+      <c r="BM51" s="10" t="n"/>
+      <c r="BN51" s="10" t="n"/>
+      <c r="BO51" s="10" t="n"/>
+      <c r="BP51" s="10" t="n"/>
+      <c r="BQ51" s="11" t="n"/>
+    </row>
+    <row r="52" ht="144" customHeight="1">
+      <c r="A52" s="44" t="n">
+        <v>35</v>
+      </c>
+      <c r="B52" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-013-035</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="46" t="inlineStr">
+        <is>
+          <t>Logic nghiệp vụ — Luồng hủy lịch sử thành công (thêm dòng đỏ và tính lại master)</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="11" t="n"/>
+      <c r="J52" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (thuộc ja_id=100, có quyền `dokusya.update`)
+・Người đọc bản giấy có dòng cuối chuỗi với ngày áp dụng ở tương lai (ví dụ: tăng số bản đọc từ 1 lên 3)
+・Số bản đọc trong `t_dokusya` trước khi hủy là 1</t>
+        </is>
+      </c>
+      <c r="K52" s="10" t="n"/>
+      <c r="L52" s="10" t="n"/>
+      <c r="M52" s="10" t="n"/>
+      <c r="N52" s="10" t="n"/>
+      <c r="O52" s="10" t="n"/>
+      <c r="P52" s="11" t="n"/>
+      <c r="Q52" s="46" t="inlineStr"/>
+      <c r="R52" s="10" t="n"/>
+      <c r="S52" s="10" t="n"/>
+      <c r="T52" s="10" t="n"/>
+      <c r="U52" s="10" t="n"/>
+      <c r="V52" s="10" t="n"/>
+      <c r="W52" s="11" t="n"/>
+      <c r="X52" s="46" t="inlineStr"/>
+      <c r="Y52" s="10" t="n"/>
+      <c r="Z52" s="10" t="n"/>
+      <c r="AA52" s="10" t="n"/>
+      <c r="AB52" s="10" t="n"/>
+      <c r="AC52" s="10" t="n"/>
+      <c r="AD52" s="11" t="n"/>
+      <c r="AE52" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF52" s="11" t="n"/>
+      <c r="AG52" s="45" t="inlineStr"/>
+      <c r="AH52" s="10" t="n"/>
+      <c r="AI52" s="11" t="n"/>
+      <c r="AJ52" s="45" t="inlineStr"/>
+      <c r="AK52" s="10" t="n"/>
+      <c r="AL52" s="11" t="n"/>
+      <c r="AM52" s="45" t="inlineStr"/>
+      <c r="AN52" s="10" t="n"/>
+      <c r="AO52" s="11" t="n"/>
+      <c r="AP52" s="45" t="inlineStr"/>
+      <c r="AQ52" s="10" t="n"/>
+      <c r="AR52" s="11" t="n"/>
+      <c r="AS52" s="45" t="inlineStr"/>
+      <c r="AT52" s="10" t="n"/>
+      <c r="AU52" s="11" t="n"/>
+      <c r="AV52" s="45" t="inlineStr"/>
+      <c r="AW52" s="10" t="n"/>
+      <c r="AX52" s="11" t="n"/>
+      <c r="AY52" s="45" t="inlineStr"/>
+      <c r="AZ52" s="10" t="n"/>
+      <c r="BA52" s="11" t="n"/>
+      <c r="BB52" s="45" t="inlineStr"/>
+      <c r="BC52" s="10" t="n"/>
+      <c r="BD52" s="11" t="n"/>
+      <c r="BE52" s="45" t="inlineStr"/>
+      <c r="BF52" s="10" t="n"/>
+      <c r="BG52" s="11" t="n"/>
+      <c r="BH52" s="45" t="inlineStr"/>
+      <c r="BI52" s="10" t="n"/>
+      <c r="BJ52" s="11" t="n"/>
+      <c r="BK52" s="46" t="inlineStr"/>
+      <c r="BL52" s="10" t="n"/>
+      <c r="BM52" s="10" t="n"/>
+      <c r="BN52" s="10" t="n"/>
+      <c r="BO52" s="10" t="n"/>
+      <c r="BP52" s="10" t="n"/>
+      <c r="BQ52" s="11" t="n"/>
+    </row>
+    <row r="53" ht="96" customHeight="1">
+      <c r="A53" s="44" t="n">
+        <v>36</v>
+      </c>
+      <c r="B53" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-013-036</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="11" t="n"/>
+      <c r="E53" s="46" t="inlineStr">
+        <is>
+          <t>Kiểm tra input — Lý do hủy bắt buộc và độ dài tối đa</t>
+        </is>
+      </c>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
+      <c r="H53" s="10" t="n"/>
+      <c r="I53" s="11" t="n"/>
+      <c r="J53" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (thuộc ja_id=100, có quyền `dokusya.update`)
+・Tồn tại dòng lịch sử có thể hủy (dòng cuối bản giấy có ngày áp dụng ở tương lai)</t>
+        </is>
+      </c>
+      <c r="K53" s="10" t="n"/>
+      <c r="L53" s="10" t="n"/>
+      <c r="M53" s="10" t="n"/>
+      <c r="N53" s="10" t="n"/>
+      <c r="O53" s="10" t="n"/>
+      <c r="P53" s="11" t="n"/>
+      <c r="Q53" s="46" t="inlineStr"/>
+      <c r="R53" s="10" t="n"/>
+      <c r="S53" s="10" t="n"/>
+      <c r="T53" s="10" t="n"/>
+      <c r="U53" s="10" t="n"/>
+      <c r="V53" s="10" t="n"/>
+      <c r="W53" s="11" t="n"/>
+      <c r="X53" s="46" t="inlineStr"/>
+      <c r="Y53" s="10" t="n"/>
+      <c r="Z53" s="10" t="n"/>
+      <c r="AA53" s="10" t="n"/>
+      <c r="AB53" s="10" t="n"/>
+      <c r="AC53" s="10" t="n"/>
+      <c r="AD53" s="11" t="n"/>
+      <c r="AE53" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF53" s="11" t="n"/>
+      <c r="AG53" s="45" t="inlineStr"/>
+      <c r="AH53" s="10" t="n"/>
+      <c r="AI53" s="11" t="n"/>
+      <c r="AJ53" s="45" t="inlineStr"/>
+      <c r="AK53" s="10" t="n"/>
+      <c r="AL53" s="11" t="n"/>
+      <c r="AM53" s="45" t="inlineStr"/>
+      <c r="AN53" s="10" t="n"/>
+      <c r="AO53" s="11" t="n"/>
+      <c r="AP53" s="45" t="inlineStr"/>
+      <c r="AQ53" s="10" t="n"/>
+      <c r="AR53" s="11" t="n"/>
+      <c r="AS53" s="45" t="inlineStr"/>
+      <c r="AT53" s="10" t="n"/>
+      <c r="AU53" s="11" t="n"/>
+      <c r="AV53" s="45" t="inlineStr"/>
+      <c r="AW53" s="10" t="n"/>
+      <c r="AX53" s="11" t="n"/>
+      <c r="AY53" s="45" t="inlineStr"/>
+      <c r="AZ53" s="10" t="n"/>
+      <c r="BA53" s="11" t="n"/>
+      <c r="BB53" s="45" t="inlineStr"/>
+      <c r="BC53" s="10" t="n"/>
+      <c r="BD53" s="11" t="n"/>
+      <c r="BE53" s="45" t="inlineStr"/>
+      <c r="BF53" s="10" t="n"/>
+      <c r="BG53" s="11" t="n"/>
+      <c r="BH53" s="45" t="inlineStr"/>
+      <c r="BI53" s="10" t="n"/>
+      <c r="BJ53" s="11" t="n"/>
+      <c r="BK53" s="46" t="inlineStr"/>
+      <c r="BL53" s="10" t="n"/>
+      <c r="BM53" s="10" t="n"/>
+      <c r="BN53" s="10" t="n"/>
+      <c r="BO53" s="10" t="n"/>
+      <c r="BP53" s="10" t="n"/>
+      <c r="BQ53" s="11" t="n"/>
+    </row>
+    <row r="54" ht="160" customHeight="1">
+      <c r="A54" s="44" t="n">
+        <v>37</v>
+      </c>
+      <c r="B54" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-013-037</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="46" t="inlineStr">
+        <is>
+          <t>Logic nghiệp vụ — Gọi API trực tiếp vào bản ghi không được hủy (TORIKESHI_NOT_ALLOWED)</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="11" t="n"/>
+      <c r="J54" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (thuộc ja_id=100, có quyền `dokusya.update`)
+・Tồn tại các dòng lịch sử (a)〜(e) giống ACSMS-TC-013-034
+・Có thể gọi API trực tiếp mà không đi qua nút bị vô hiệu hóa trên màn hình (curl / DevTools)</t>
+        </is>
+      </c>
+      <c r="K54" s="10" t="n"/>
+      <c r="L54" s="10" t="n"/>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="10" t="n"/>
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="11" t="n"/>
+      <c r="Q54" s="46" t="inlineStr"/>
+      <c r="R54" s="10" t="n"/>
+      <c r="S54" s="10" t="n"/>
+      <c r="T54" s="10" t="n"/>
+      <c r="U54" s="10" t="n"/>
+      <c r="V54" s="10" t="n"/>
+      <c r="W54" s="11" t="n"/>
+      <c r="X54" s="46" t="inlineStr"/>
+      <c r="Y54" s="10" t="n"/>
+      <c r="Z54" s="10" t="n"/>
+      <c r="AA54" s="10" t="n"/>
+      <c r="AB54" s="10" t="n"/>
+      <c r="AC54" s="10" t="n"/>
+      <c r="AD54" s="11" t="n"/>
+      <c r="AE54" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF54" s="11" t="n"/>
+      <c r="AG54" s="45" t="inlineStr"/>
+      <c r="AH54" s="10" t="n"/>
+      <c r="AI54" s="11" t="n"/>
+      <c r="AJ54" s="45" t="inlineStr"/>
+      <c r="AK54" s="10" t="n"/>
+      <c r="AL54" s="11" t="n"/>
+      <c r="AM54" s="45" t="inlineStr"/>
+      <c r="AN54" s="10" t="n"/>
+      <c r="AO54" s="11" t="n"/>
+      <c r="AP54" s="45" t="inlineStr"/>
+      <c r="AQ54" s="10" t="n"/>
+      <c r="AR54" s="11" t="n"/>
+      <c r="AS54" s="45" t="inlineStr"/>
+      <c r="AT54" s="10" t="n"/>
+      <c r="AU54" s="11" t="n"/>
+      <c r="AV54" s="45" t="inlineStr"/>
+      <c r="AW54" s="10" t="n"/>
+      <c r="AX54" s="11" t="n"/>
+      <c r="AY54" s="45" t="inlineStr"/>
+      <c r="AZ54" s="10" t="n"/>
+      <c r="BA54" s="11" t="n"/>
+      <c r="BB54" s="45" t="inlineStr"/>
+      <c r="BC54" s="10" t="n"/>
+      <c r="BD54" s="11" t="n"/>
+      <c r="BE54" s="45" t="inlineStr"/>
+      <c r="BF54" s="10" t="n"/>
+      <c r="BG54" s="11" t="n"/>
+      <c r="BH54" s="45" t="inlineStr"/>
+      <c r="BI54" s="10" t="n"/>
+      <c r="BJ54" s="11" t="n"/>
+      <c r="BK54" s="46" t="inlineStr"/>
+      <c r="BL54" s="10" t="n"/>
+      <c r="BM54" s="10" t="n"/>
+      <c r="BN54" s="10" t="n"/>
+      <c r="BO54" s="10" t="n"/>
+      <c r="BP54" s="10" t="n"/>
+      <c r="BQ54" s="11" t="n"/>
+    </row>
+    <row r="55" ht="144" customHeight="1">
+      <c r="A55" s="44" t="n">
+        <v>38</v>
+      </c>
+      <c r="B55" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-013-038</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="11" t="n"/>
+      <c r="E55" s="46" t="inlineStr">
+        <is>
+          <t>Kiểm soát quyền truy cập — DataScope và kiểm tra quyền sở hữu dòng lịch sử của API hủy</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="n"/>
+      <c r="G55" s="10" t="n"/>
+      <c r="H55" s="10" t="n"/>
+      <c r="I55" s="11" t="n"/>
+      <c r="J55" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (thuộc ja_id=100, có quyền `dokusya.update`)
+・JA của mình (ja_id=100) có người đọc A sở hữu dòng lịch sử có thể hủy
+・JA khác (ja_id=200) có người đọc B sở hữu dòng lịch sử có thể hủy</t>
+        </is>
+      </c>
+      <c r="K55" s="10" t="n"/>
+      <c r="L55" s="10" t="n"/>
+      <c r="M55" s="10" t="n"/>
+      <c r="N55" s="10" t="n"/>
+      <c r="O55" s="10" t="n"/>
+      <c r="P55" s="11" t="n"/>
+      <c r="Q55" s="46" t="inlineStr"/>
+      <c r="R55" s="10" t="n"/>
+      <c r="S55" s="10" t="n"/>
+      <c r="T55" s="10" t="n"/>
+      <c r="U55" s="10" t="n"/>
+      <c r="V55" s="10" t="n"/>
+      <c r="W55" s="11" t="n"/>
+      <c r="X55" s="46" t="inlineStr"/>
+      <c r="Y55" s="10" t="n"/>
+      <c r="Z55" s="10" t="n"/>
+      <c r="AA55" s="10" t="n"/>
+      <c r="AB55" s="10" t="n"/>
+      <c r="AC55" s="10" t="n"/>
+      <c r="AD55" s="11" t="n"/>
+      <c r="AE55" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF55" s="11" t="n"/>
+      <c r="AG55" s="45" t="inlineStr"/>
+      <c r="AH55" s="10" t="n"/>
+      <c r="AI55" s="11" t="n"/>
+      <c r="AJ55" s="45" t="inlineStr"/>
+      <c r="AK55" s="10" t="n"/>
+      <c r="AL55" s="11" t="n"/>
+      <c r="AM55" s="45" t="inlineStr"/>
+      <c r="AN55" s="10" t="n"/>
+      <c r="AO55" s="11" t="n"/>
+      <c r="AP55" s="45" t="inlineStr"/>
+      <c r="AQ55" s="10" t="n"/>
+      <c r="AR55" s="11" t="n"/>
+      <c r="AS55" s="45" t="inlineStr"/>
+      <c r="AT55" s="10" t="n"/>
+      <c r="AU55" s="11" t="n"/>
+      <c r="AV55" s="45" t="inlineStr"/>
+      <c r="AW55" s="10" t="n"/>
+      <c r="AX55" s="11" t="n"/>
+      <c r="AY55" s="45" t="inlineStr"/>
+      <c r="AZ55" s="10" t="n"/>
+      <c r="BA55" s="11" t="n"/>
+      <c r="BB55" s="45" t="inlineStr"/>
+      <c r="BC55" s="10" t="n"/>
+      <c r="BD55" s="11" t="n"/>
+      <c r="BE55" s="45" t="inlineStr"/>
+      <c r="BF55" s="10" t="n"/>
+      <c r="BG55" s="11" t="n"/>
+      <c r="BH55" s="45" t="inlineStr"/>
+      <c r="BI55" s="10" t="n"/>
+      <c r="BJ55" s="11" t="n"/>
+      <c r="BK55" s="46" t="inlineStr"/>
+      <c r="BL55" s="10" t="n"/>
+      <c r="BM55" s="10" t="n"/>
+      <c r="BN55" s="10" t="n"/>
+      <c r="BO55" s="10" t="n"/>
+      <c r="BP55" s="10" t="n"/>
+      <c r="BQ55" s="11" t="n"/>
+    </row>
+    <row r="56" ht="80" customHeight="1">
+      <c r="A56" s="44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B56" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-013-039</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="46" t="inlineStr">
+        <is>
+          <t>Hiển thị màn hình — Hiển thị dòng đã hủy (gạch ngang) và vị trí dòng đỏ</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
+      <c r="H56" s="10" t="n"/>
+      <c r="I56" s="11" t="n"/>
+      <c r="J56" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (thuộc ja_id=100)
+・Đã thực hiện ACSMS-TC-013-035, tồn tại dòng đã hủy và dòng đỏ</t>
+        </is>
+      </c>
+      <c r="K56" s="10" t="n"/>
+      <c r="L56" s="10" t="n"/>
+      <c r="M56" s="10" t="n"/>
+      <c r="N56" s="10" t="n"/>
+      <c r="O56" s="10" t="n"/>
+      <c r="P56" s="11" t="n"/>
+      <c r="Q56" s="46" t="inlineStr"/>
+      <c r="R56" s="10" t="n"/>
+      <c r="S56" s="10" t="n"/>
+      <c r="T56" s="10" t="n"/>
+      <c r="U56" s="10" t="n"/>
+      <c r="V56" s="10" t="n"/>
+      <c r="W56" s="11" t="n"/>
+      <c r="X56" s="46" t="inlineStr"/>
+      <c r="Y56" s="10" t="n"/>
+      <c r="Z56" s="10" t="n"/>
+      <c r="AA56" s="10" t="n"/>
+      <c r="AB56" s="10" t="n"/>
+      <c r="AC56" s="10" t="n"/>
+      <c r="AD56" s="11" t="n"/>
+      <c r="AE56" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF56" s="11" t="n"/>
+      <c r="AG56" s="45" t="inlineStr"/>
+      <c r="AH56" s="10" t="n"/>
+      <c r="AI56" s="11" t="n"/>
+      <c r="AJ56" s="45" t="inlineStr"/>
+      <c r="AK56" s="10" t="n"/>
+      <c r="AL56" s="11" t="n"/>
+      <c r="AM56" s="45" t="inlineStr"/>
+      <c r="AN56" s="10" t="n"/>
+      <c r="AO56" s="11" t="n"/>
+      <c r="AP56" s="45" t="inlineStr"/>
+      <c r="AQ56" s="10" t="n"/>
+      <c r="AR56" s="11" t="n"/>
+      <c r="AS56" s="45" t="inlineStr"/>
+      <c r="AT56" s="10" t="n"/>
+      <c r="AU56" s="11" t="n"/>
+      <c r="AV56" s="45" t="inlineStr"/>
+      <c r="AW56" s="10" t="n"/>
+      <c r="AX56" s="11" t="n"/>
+      <c r="AY56" s="45" t="inlineStr"/>
+      <c r="AZ56" s="10" t="n"/>
+      <c r="BA56" s="11" t="n"/>
+      <c r="BB56" s="45" t="inlineStr"/>
+      <c r="BC56" s="10" t="n"/>
+      <c r="BD56" s="11" t="n"/>
+      <c r="BE56" s="45" t="inlineStr"/>
+      <c r="BF56" s="10" t="n"/>
+      <c r="BG56" s="11" t="n"/>
+      <c r="BH56" s="45" t="inlineStr"/>
+      <c r="BI56" s="10" t="n"/>
+      <c r="BJ56" s="11" t="n"/>
+      <c r="BK56" s="46" t="inlineStr"/>
+      <c r="BL56" s="10" t="n"/>
+      <c r="BM56" s="10" t="n"/>
+      <c r="BN56" s="10" t="n"/>
+      <c r="BO56" s="10" t="n"/>
+      <c r="BP56" s="10" t="n"/>
+      <c r="BQ56" s="11" t="n"/>
+    </row>
+    <row r="57" ht="128" customHeight="1">
+      <c r="A57" s="44" t="n">
+        <v>40</v>
+      </c>
+      <c r="B57" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-013-040</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="11" t="n"/>
+      <c r="E57" s="46" t="inlineStr">
+        <is>
+          <t>Hiển thị màn hình — Nội dung cột người tạo (created_by) (#55719)</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="11" t="n"/>
+      <c r="J57" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (thuộc ja_id=100)
+・Tồn tại dòng lịch sử được tạo bằng thao tác trên màn hình
+・Tồn tại dòng lịch sử được tạo bởi batch đồng bộ người đọc (liên kết bản điện tử)</t>
+        </is>
+      </c>
+      <c r="K57" s="10" t="n"/>
+      <c r="L57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="11" t="n"/>
+      <c r="Q57" s="46" t="inlineStr"/>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
+      <c r="W57" s="11" t="n"/>
+      <c r="X57" s="46" t="inlineStr"/>
+      <c r="Y57" s="10" t="n"/>
+      <c r="Z57" s="10" t="n"/>
+      <c r="AA57" s="10" t="n"/>
+      <c r="AB57" s="10" t="n"/>
+      <c r="AC57" s="10" t="n"/>
+      <c r="AD57" s="11" t="n"/>
+      <c r="AE57" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF57" s="11" t="n"/>
+      <c r="AG57" s="45" t="inlineStr"/>
+      <c r="AH57" s="10" t="n"/>
+      <c r="AI57" s="11" t="n"/>
+      <c r="AJ57" s="45" t="inlineStr"/>
+      <c r="AK57" s="10" t="n"/>
+      <c r="AL57" s="11" t="n"/>
+      <c r="AM57" s="45" t="inlineStr"/>
+      <c r="AN57" s="10" t="n"/>
+      <c r="AO57" s="11" t="n"/>
+      <c r="AP57" s="45" t="inlineStr"/>
+      <c r="AQ57" s="10" t="n"/>
+      <c r="AR57" s="11" t="n"/>
+      <c r="AS57" s="45" t="inlineStr"/>
+      <c r="AT57" s="10" t="n"/>
+      <c r="AU57" s="11" t="n"/>
+      <c r="AV57" s="45" t="inlineStr"/>
+      <c r="AW57" s="10" t="n"/>
+      <c r="AX57" s="11" t="n"/>
+      <c r="AY57" s="45" t="inlineStr"/>
+      <c r="AZ57" s="10" t="n"/>
+      <c r="BA57" s="11" t="n"/>
+      <c r="BB57" s="45" t="inlineStr"/>
+      <c r="BC57" s="10" t="n"/>
+      <c r="BD57" s="11" t="n"/>
+      <c r="BE57" s="45" t="inlineStr"/>
+      <c r="BF57" s="10" t="n"/>
+      <c r="BG57" s="11" t="n"/>
+      <c r="BH57" s="45" t="inlineStr"/>
+      <c r="BI57" s="10" t="n"/>
+      <c r="BJ57" s="11" t="n"/>
+      <c r="BK57" s="46" t="inlineStr"/>
+      <c r="BL57" s="10" t="n"/>
+      <c r="BM57" s="10" t="n"/>
+      <c r="BN57" s="10" t="n"/>
+      <c r="BO57" s="10" t="n"/>
+      <c r="BP57" s="10" t="n"/>
+      <c r="BQ57" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="632">
+  <mergeCells count="752">
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="AS46:AU46"/>
+    <mergeCell ref="AE54:AF54"/>
     <mergeCell ref="BH33:BJ33"/>
+    <mergeCell ref="E52:I52"/>
     <mergeCell ref="AE41:AF41"/>
+    <mergeCell ref="AV57:AX57"/>
+    <mergeCell ref="B53:D53"/>
     <mergeCell ref="E39:I39"/>
     <mergeCell ref="E14:I14"/>
     <mergeCell ref="W7:Y7"/>
     <mergeCell ref="AS48:AU48"/>
     <mergeCell ref="BK16:BQ16"/>
+    <mergeCell ref="AE56:AF56"/>
     <mergeCell ref="AE43:AF43"/>
     <mergeCell ref="AM30:AO30"/>
     <mergeCell ref="AP45:AR45"/>
@@ -14668,6 +15448,7 @@
     <mergeCell ref="AM21:AO21"/>
     <mergeCell ref="AG24:AI24"/>
     <mergeCell ref="BH39:BJ39"/>
+    <mergeCell ref="J57:P57"/>
     <mergeCell ref="W2:AH2"/>
     <mergeCell ref="X10:AD11"/>
     <mergeCell ref="AJ22:AL22"/>
@@ -14675,10 +15456,12 @@
     <mergeCell ref="AP13:AR13"/>
     <mergeCell ref="Q38:W38"/>
     <mergeCell ref="AE34:AF34"/>
+    <mergeCell ref="AJ51:AL51"/>
     <mergeCell ref="BK47:BQ47"/>
     <mergeCell ref="E25:I25"/>
     <mergeCell ref="Q40:W40"/>
     <mergeCell ref="AE36:AF36"/>
+    <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="Q15:W15"/>
     <mergeCell ref="AV39:AX39"/>
     <mergeCell ref="BH21:BJ21"/>
@@ -14686,6 +15469,7 @@
     <mergeCell ref="AJ38:AL38"/>
     <mergeCell ref="BK48:BQ48"/>
     <mergeCell ref="AM49:AO49"/>
+    <mergeCell ref="AG52:AI52"/>
     <mergeCell ref="BE22:BG22"/>
     <mergeCell ref="BH23:BJ23"/>
     <mergeCell ref="BB26:BD26"/>
@@ -14701,13 +15485,17 @@
     <mergeCell ref="AF8:AH8"/>
     <mergeCell ref="AY31:BA31"/>
     <mergeCell ref="BK37:BQ37"/>
+    <mergeCell ref="AM55:AO55"/>
     <mergeCell ref="BH34:BJ34"/>
     <mergeCell ref="X23:AD23"/>
     <mergeCell ref="BE38:BG38"/>
     <mergeCell ref="BH49:BJ49"/>
     <mergeCell ref="R3:V3"/>
+    <mergeCell ref="AP53:AR53"/>
     <mergeCell ref="X16:AD16"/>
     <mergeCell ref="AP28:AR28"/>
+    <mergeCell ref="AE57:AF57"/>
+    <mergeCell ref="BK53:BQ53"/>
     <mergeCell ref="AC7:AE7"/>
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
@@ -14716,9 +15504,11 @@
     <mergeCell ref="BB37:BD37"/>
     <mergeCell ref="BK13:BQ13"/>
     <mergeCell ref="B21:D21"/>
+    <mergeCell ref="AY57:BA57"/>
     <mergeCell ref="BE41:BG41"/>
     <mergeCell ref="J25:P25"/>
     <mergeCell ref="Q46:W46"/>
+    <mergeCell ref="BH55:BJ55"/>
     <mergeCell ref="AM24:AO24"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="BB38:BD38"/>
@@ -14733,11 +15523,16 @@
     <mergeCell ref="BH29:BJ29"/>
     <mergeCell ref="Q41:W41"/>
     <mergeCell ref="AY44:BA44"/>
+    <mergeCell ref="AV53:AX53"/>
     <mergeCell ref="BH44:BJ44"/>
     <mergeCell ref="AS19:AU19"/>
+    <mergeCell ref="Q56:W56"/>
+    <mergeCell ref="AE52:AF52"/>
     <mergeCell ref="Q43:W43"/>
     <mergeCell ref="J14:P14"/>
     <mergeCell ref="AE39:AF39"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="AJ54:AL54"/>
     <mergeCell ref="AM15:AO15"/>
     <mergeCell ref="AP16:AR16"/>
     <mergeCell ref="BH24:BJ24"/>
@@ -14747,14 +15542,19 @@
     <mergeCell ref="AJ41:AL41"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="BK10:BQ11"/>
+    <mergeCell ref="J53:P53"/>
     <mergeCell ref="AS14:AU14"/>
+    <mergeCell ref="AE53:AF53"/>
+    <mergeCell ref="AG55:AI55"/>
     <mergeCell ref="AP18:AR18"/>
+    <mergeCell ref="AJ56:AL56"/>
     <mergeCell ref="BH26:BJ26"/>
     <mergeCell ref="AG38:AI38"/>
     <mergeCell ref="BE30:BG30"/>
     <mergeCell ref="AJ43:AL43"/>
     <mergeCell ref="AV25:AX25"/>
     <mergeCell ref="W6:Y6"/>
+    <mergeCell ref="J55:P55"/>
     <mergeCell ref="BE29:BG29"/>
     <mergeCell ref="BK28:BQ28"/>
     <mergeCell ref="AY32:BA32"/>
@@ -14767,6 +15567,7 @@
     <mergeCell ref="AY47:BA47"/>
     <mergeCell ref="E21:I21"/>
     <mergeCell ref="Q36:W36"/>
+    <mergeCell ref="BE54:BG54"/>
     <mergeCell ref="Q30:W30"/>
     <mergeCell ref="X26:AD26"/>
     <mergeCell ref="W1:AH1"/>
@@ -14774,9 +15575,11 @@
     <mergeCell ref="AP44:AR44"/>
     <mergeCell ref="E23:I23"/>
     <mergeCell ref="B29:D29"/>
+    <mergeCell ref="BE56:BG56"/>
     <mergeCell ref="BE43:BG43"/>
     <mergeCell ref="J33:P33"/>
     <mergeCell ref="BB46:BD46"/>
+    <mergeCell ref="BE57:BG57"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="AV15:AX15"/>
     <mergeCell ref="AY16:BA16"/>
@@ -14790,6 +15593,7 @@
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="AY45:BA45"/>
     <mergeCell ref="E36:I36"/>
+    <mergeCell ref="Q51:W51"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="BH45:BJ45"/>
     <mergeCell ref="AP24:AR24"/>
@@ -14800,11 +15604,13 @@
     <mergeCell ref="AS22:AU22"/>
     <mergeCell ref="AP26:AR26"/>
     <mergeCell ref="X14:AD14"/>
+    <mergeCell ref="AE55:AF55"/>
     <mergeCell ref="AG21:AI21"/>
     <mergeCell ref="X38:AD38"/>
     <mergeCell ref="BH46:BJ46"/>
     <mergeCell ref="BE44:BG44"/>
     <mergeCell ref="AP19:AR19"/>
+    <mergeCell ref="AJ57:AL57"/>
     <mergeCell ref="BE31:BG31"/>
     <mergeCell ref="J21:P21"/>
     <mergeCell ref="A1:E1"/>
@@ -14827,6 +15633,7 @@
     <mergeCell ref="AV36:AX36"/>
     <mergeCell ref="T6:V6"/>
     <mergeCell ref="AV30:AX30"/>
+    <mergeCell ref="Q52:W52"/>
     <mergeCell ref="Q39:W39"/>
     <mergeCell ref="AS33:AU33"/>
     <mergeCell ref="AM36:AO36"/>
@@ -14840,12 +15647,16 @@
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
     <mergeCell ref="AV21:AX21"/>
+    <mergeCell ref="AY53:BA53"/>
     <mergeCell ref="BK24:BQ24"/>
     <mergeCell ref="X45:AD45"/>
     <mergeCell ref="AG11:AI11"/>
+    <mergeCell ref="BH53:BJ53"/>
     <mergeCell ref="AV29:AX29"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="AV23:AX23"/>
+    <mergeCell ref="BB51:BD51"/>
+    <mergeCell ref="AY55:BA55"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="E44:I44"/>
     <mergeCell ref="BK19:BQ19"/>
@@ -14867,29 +15678,39 @@
     <mergeCell ref="BB11:BD11"/>
     <mergeCell ref="AJ25:AL25"/>
     <mergeCell ref="B45:D45"/>
+    <mergeCell ref="BE53:BG53"/>
     <mergeCell ref="AM32:AO32"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="AM26:AO26"/>
     <mergeCell ref="J24:P24"/>
+    <mergeCell ref="AG51:AI51"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="Q14:W14"/>
+    <mergeCell ref="E57:I57"/>
     <mergeCell ref="B46:D46"/>
+    <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="E32:I32"/>
     <mergeCell ref="J26:P26"/>
     <mergeCell ref="AS41:AU41"/>
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="AV55:AX55"/>
     <mergeCell ref="E47:I47"/>
     <mergeCell ref="BB39:BD39"/>
     <mergeCell ref="B48:D48"/>
+    <mergeCell ref="AV52:AX52"/>
+    <mergeCell ref="AP55:AR55"/>
+    <mergeCell ref="AS56:AU56"/>
     <mergeCell ref="AP38:AR38"/>
     <mergeCell ref="X41:AD41"/>
     <mergeCell ref="AS43:AU43"/>
     <mergeCell ref="BE25:BG25"/>
     <mergeCell ref="BK38:BQ38"/>
     <mergeCell ref="F4:AH4"/>
+    <mergeCell ref="X51:AD51"/>
     <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="AM52:AO52"/>
     <mergeCell ref="AG17:AI17"/>
     <mergeCell ref="AS36:AU36"/>
     <mergeCell ref="AM39:AO39"/>
@@ -14898,6 +15719,7 @@
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="AG19:AI19"/>
     <mergeCell ref="X36:AD36"/>
+    <mergeCell ref="J52:P52"/>
     <mergeCell ref="J44:P44"/>
     <mergeCell ref="Q25:W25"/>
     <mergeCell ref="AV37:AX37"/>
@@ -14919,6 +15741,7 @@
     <mergeCell ref="AM23:AO23"/>
     <mergeCell ref="AE24:AF24"/>
     <mergeCell ref="AS44:AU44"/>
+    <mergeCell ref="BE55:BG55"/>
     <mergeCell ref="AS31:AU31"/>
     <mergeCell ref="BH18:BJ18"/>
     <mergeCell ref="J32:P32"/>
@@ -14930,11 +15753,13 @@
     <mergeCell ref="AY24:BA24"/>
     <mergeCell ref="AJ28:AL28"/>
     <mergeCell ref="BK17:BQ17"/>
+    <mergeCell ref="BK55:BQ55"/>
     <mergeCell ref="AP30:AR30"/>
     <mergeCell ref="AJ30:AL30"/>
     <mergeCell ref="AP46:AR46"/>
     <mergeCell ref="BK46:BQ46"/>
     <mergeCell ref="BK40:BQ40"/>
+    <mergeCell ref="AS57:AU57"/>
     <mergeCell ref="AY19:BA19"/>
     <mergeCell ref="BK25:BQ25"/>
     <mergeCell ref="Q21:W21"/>
@@ -14942,14 +15767,17 @@
     <mergeCell ref="AP48:AR48"/>
     <mergeCell ref="A27:BQ27"/>
     <mergeCell ref="AE44:AF44"/>
+    <mergeCell ref="X57:AD57"/>
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="AP41:AR41"/>
     <mergeCell ref="AM18:AO18"/>
     <mergeCell ref="BK41:BQ41"/>
     <mergeCell ref="BB13:BD13"/>
     <mergeCell ref="AM17:AO17"/>
+    <mergeCell ref="AP56:AR56"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="AP43:AR43"/>
+    <mergeCell ref="AM53:AO53"/>
     <mergeCell ref="AM47:AO47"/>
     <mergeCell ref="B10:D11"/>
     <mergeCell ref="J45:P45"/>
@@ -14958,15 +15786,19 @@
     <mergeCell ref="AG22:AI22"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="AJ23:AL23"/>
+    <mergeCell ref="E53:I53"/>
     <mergeCell ref="AM48:AO48"/>
     <mergeCell ref="Q49:W49"/>
     <mergeCell ref="BK43:BQ43"/>
     <mergeCell ref="AM44:AO44"/>
+    <mergeCell ref="B57:D57"/>
     <mergeCell ref="AF6:AH6"/>
+    <mergeCell ref="E55:I55"/>
     <mergeCell ref="AE32:AF32"/>
     <mergeCell ref="AV48:AX48"/>
     <mergeCell ref="AY14:BA14"/>
     <mergeCell ref="AJ18:AL18"/>
+    <mergeCell ref="J51:P51"/>
     <mergeCell ref="F2:Q2"/>
     <mergeCell ref="AS39:AU39"/>
     <mergeCell ref="BH17:BJ17"/>
@@ -14987,13 +15819,16 @@
     <mergeCell ref="BK30:BQ30"/>
     <mergeCell ref="BK36:BQ36"/>
     <mergeCell ref="AS47:AU47"/>
+    <mergeCell ref="AY54:BA54"/>
     <mergeCell ref="AJ29:AL29"/>
     <mergeCell ref="AG33:AI33"/>
     <mergeCell ref="X17:AD17"/>
     <mergeCell ref="AJ44:AL44"/>
+    <mergeCell ref="Q54:W54"/>
     <mergeCell ref="BE18:BG18"/>
     <mergeCell ref="AJ31:AL31"/>
     <mergeCell ref="Q29:W29"/>
+    <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
     <mergeCell ref="X19:AD19"/>
     <mergeCell ref="AG34:AI34"/>
@@ -15002,21 +15837,27 @@
     <mergeCell ref="Q31:W31"/>
     <mergeCell ref="BE49:BG49"/>
     <mergeCell ref="E10:I11"/>
+    <mergeCell ref="BK56:BQ56"/>
     <mergeCell ref="BE36:BG36"/>
     <mergeCell ref="BH37:BJ37"/>
     <mergeCell ref="AE45:AF45"/>
     <mergeCell ref="Z7:AB7"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="R1:V1"/>
+    <mergeCell ref="AP51:AR51"/>
+    <mergeCell ref="BK51:BQ51"/>
     <mergeCell ref="B17:D17"/>
+    <mergeCell ref="BB54:BD54"/>
     <mergeCell ref="AE22:AF22"/>
     <mergeCell ref="BB41:BD41"/>
     <mergeCell ref="J46:P46"/>
     <mergeCell ref="AE46:AF46"/>
+    <mergeCell ref="BH51:BJ51"/>
     <mergeCell ref="Z8:AB8"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="AY11:BA11"/>
+    <mergeCell ref="Q57:W57"/>
     <mergeCell ref="J48:P48"/>
     <mergeCell ref="AJ26:AL26"/>
     <mergeCell ref="AS13:AU13"/>
@@ -15024,12 +15865,15 @@
     <mergeCell ref="AY40:BA40"/>
     <mergeCell ref="A12:BQ12"/>
     <mergeCell ref="AY15:BA15"/>
+    <mergeCell ref="AS53:AU53"/>
     <mergeCell ref="AG23:AI23"/>
     <mergeCell ref="BH40:BJ40"/>
     <mergeCell ref="X13:AD13"/>
     <mergeCell ref="AS15:AU15"/>
     <mergeCell ref="AE48:AF48"/>
+    <mergeCell ref="AS55:AU55"/>
     <mergeCell ref="BE37:BG37"/>
+    <mergeCell ref="AG54:AI54"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="BE24:BG24"/>
     <mergeCell ref="BH25:BJ25"/>
@@ -15038,7 +15882,10 @@
     <mergeCell ref="AG41:AI41"/>
     <mergeCell ref="AP39:AR39"/>
     <mergeCell ref="AP14:AR14"/>
+    <mergeCell ref="AJ52:AL52"/>
     <mergeCell ref="BH22:BJ22"/>
+    <mergeCell ref="BK52:BQ52"/>
+    <mergeCell ref="AG56:AI56"/>
     <mergeCell ref="BE26:BG26"/>
     <mergeCell ref="J16:P16"/>
     <mergeCell ref="AJ39:AL39"/>
@@ -15050,6 +15897,7 @@
     <mergeCell ref="AS25:AU25"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="AG49:AI49"/>
+    <mergeCell ref="AE51:AF51"/>
     <mergeCell ref="BB29:BD29"/>
     <mergeCell ref="BB23:BD23"/>
     <mergeCell ref="E24:I24"/>
@@ -15064,7 +15912,9 @@
     <mergeCell ref="Q47:W47"/>
     <mergeCell ref="BH13:BJ13"/>
     <mergeCell ref="E19:I19"/>
+    <mergeCell ref="BE52:BG52"/>
     <mergeCell ref="BK21:BQ21"/>
+    <mergeCell ref="BB56:BD56"/>
     <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="BH15:BJ15"/>
     <mergeCell ref="AY30:BA30"/>
@@ -15072,6 +15922,7 @@
     <mergeCell ref="AP25:AR25"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="AY46:BA46"/>
+    <mergeCell ref="BB57:BD57"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="AV16:AX16"/>
     <mergeCell ref="AJ40:AL40"/>
@@ -15083,6 +15934,7 @@
     <mergeCell ref="E37:I37"/>
     <mergeCell ref="X33:AD33"/>
     <mergeCell ref="AV17:AX17"/>
+    <mergeCell ref="AY56:BA56"/>
     <mergeCell ref="AV11:AX11"/>
     <mergeCell ref="AS21:AU21"/>
     <mergeCell ref="AY43:BA43"/>
@@ -15101,13 +15953,18 @@
     <mergeCell ref="AP15:AR15"/>
     <mergeCell ref="AS16:AU16"/>
     <mergeCell ref="BB44:BD44"/>
+    <mergeCell ref="AJ53:AL53"/>
     <mergeCell ref="AV10:BJ10"/>
     <mergeCell ref="BH28:BJ28"/>
     <mergeCell ref="J17:P17"/>
+    <mergeCell ref="AM54:AO54"/>
     <mergeCell ref="AV44:AX44"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="AJ45:AL45"/>
+    <mergeCell ref="AG57:AI57"/>
     <mergeCell ref="B15:D15"/>
+    <mergeCell ref="BB52:BD52"/>
+    <mergeCell ref="AJ55:AL55"/>
     <mergeCell ref="AY34:BA34"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="J19:P19"/>
@@ -15115,6 +15972,7 @@
     <mergeCell ref="AS34:AU34"/>
     <mergeCell ref="BB45:BD45"/>
     <mergeCell ref="BB32:BD32"/>
+    <mergeCell ref="Q55:W55"/>
     <mergeCell ref="AY36:BA36"/>
     <mergeCell ref="AS49:AU49"/>
     <mergeCell ref="X34:AD34"/>
@@ -15123,21 +15981,27 @@
     <mergeCell ref="BB47:BD47"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="A35:BQ35"/>
+    <mergeCell ref="BH54:BJ54"/>
     <mergeCell ref="AP33:AR33"/>
     <mergeCell ref="BH41:BJ41"/>
     <mergeCell ref="X30:AD30"/>
     <mergeCell ref="BE45:BG45"/>
     <mergeCell ref="E22:I22"/>
+    <mergeCell ref="BH56:BJ56"/>
     <mergeCell ref="X29:AD29"/>
     <mergeCell ref="BH31:BJ31"/>
     <mergeCell ref="AJ48:AL48"/>
     <mergeCell ref="BE46:BG46"/>
+    <mergeCell ref="X54:AD54"/>
     <mergeCell ref="AY28:BA28"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="AV19:AX19"/>
     <mergeCell ref="AS23:AU23"/>
     <mergeCell ref="E38:I38"/>
+    <mergeCell ref="AY51:BA51"/>
+    <mergeCell ref="Q53:W53"/>
+    <mergeCell ref="X56:AD56"/>
     <mergeCell ref="BK22:BQ22"/>
     <mergeCell ref="E13:I13"/>
     <mergeCell ref="X43:AD43"/>
@@ -15155,21 +16019,29 @@
     <mergeCell ref="Z6:AB6"/>
     <mergeCell ref="AP21:AR21"/>
     <mergeCell ref="AS26:AU26"/>
+    <mergeCell ref="B54:D54"/>
     <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="AJ21:AL21"/>
     <mergeCell ref="AG25:AI25"/>
     <mergeCell ref="AY33:BA33"/>
+    <mergeCell ref="BB53:BD53"/>
     <mergeCell ref="T5:AH5"/>
     <mergeCell ref="AM22:AO22"/>
     <mergeCell ref="AP23:AR23"/>
+    <mergeCell ref="B56:D56"/>
     <mergeCell ref="AV47:AX47"/>
     <mergeCell ref="B43:D43"/>
+    <mergeCell ref="BE51:BG51"/>
+    <mergeCell ref="BB55:BD55"/>
     <mergeCell ref="BK33:BQ33"/>
     <mergeCell ref="A5:S5"/>
     <mergeCell ref="J22:P22"/>
     <mergeCell ref="AV38:AX38"/>
+    <mergeCell ref="AY52:BA52"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="AY39:BA39"/>
+    <mergeCell ref="AS52:AU52"/>
+    <mergeCell ref="AG53:AI53"/>
     <mergeCell ref="X44:AD44"/>
     <mergeCell ref="AP34:AR34"/>
     <mergeCell ref="AM11:AO11"/>
@@ -15178,6 +16050,7 @@
     <mergeCell ref="BB25:BD25"/>
     <mergeCell ref="AP49:AR49"/>
     <mergeCell ref="E28:I28"/>
+    <mergeCell ref="BH57:BJ57"/>
     <mergeCell ref="AG13:AI13"/>
     <mergeCell ref="AV33:AX33"/>
     <mergeCell ref="AP36:AR36"/>
@@ -15202,12 +16075,16 @@
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="X49:AD49"/>
+    <mergeCell ref="E54:I54"/>
     <mergeCell ref="AV22:AX22"/>
     <mergeCell ref="AY23:BA23"/>
     <mergeCell ref="E41:I41"/>
+    <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="F3:Q3"/>
+    <mergeCell ref="E56:I56"/>
     <mergeCell ref="AP29:AR29"/>
+    <mergeCell ref="AV51:AX51"/>
     <mergeCell ref="E43:I43"/>
     <mergeCell ref="BB15:BD15"/>
     <mergeCell ref="BE16:BG16"/>
@@ -15215,8 +16092,10 @@
     <mergeCell ref="BK23:BQ23"/>
     <mergeCell ref="AE25:AF25"/>
     <mergeCell ref="AS40:AU40"/>
+    <mergeCell ref="BH52:BJ52"/>
     <mergeCell ref="AP31:AR31"/>
     <mergeCell ref="BH14:BJ14"/>
+    <mergeCell ref="BK54:BQ54"/>
     <mergeCell ref="AJ37:AL37"/>
     <mergeCell ref="AY49:BA49"/>
     <mergeCell ref="BE11:BG11"/>
@@ -15226,18 +16105,24 @@
     <mergeCell ref="AV40:AX40"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="J28:P28"/>
+    <mergeCell ref="X52:AD52"/>
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="AG30:AI30"/>
     <mergeCell ref="Q18:W18"/>
     <mergeCell ref="BK49:BQ49"/>
+    <mergeCell ref="A50:BQ50"/>
     <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AE38:AF38"/>
+    <mergeCell ref="AV54:AX54"/>
     <mergeCell ref="A42:BQ42"/>
+    <mergeCell ref="AP57:AR57"/>
     <mergeCell ref="J30:P30"/>
     <mergeCell ref="AV41:AX41"/>
     <mergeCell ref="AE13:AF13"/>
     <mergeCell ref="AS45:AU45"/>
+    <mergeCell ref="BK57:BQ57"/>
     <mergeCell ref="AE40:AF40"/>
+    <mergeCell ref="X53:AD53"/>
     <mergeCell ref="X47:AD47"/>
     <mergeCell ref="Q19:W19"/>
     <mergeCell ref="AS38:AU38"/>
@@ -15245,18 +16130,26 @@
     <mergeCell ref="AE15:AF15"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="AM13:AO13"/>
+    <mergeCell ref="AP52:AR52"/>
+    <mergeCell ref="X55:AD55"/>
     <mergeCell ref="AJ17:AL17"/>
+    <mergeCell ref="AM56:AO56"/>
+    <mergeCell ref="J54:P54"/>
     <mergeCell ref="AM43:AO43"/>
     <mergeCell ref="J41:P41"/>
     <mergeCell ref="Q44:W44"/>
     <mergeCell ref="AV43:AX43"/>
     <mergeCell ref="AJ19:AL19"/>
+    <mergeCell ref="J56:P56"/>
     <mergeCell ref="J43:P43"/>
+    <mergeCell ref="AM57:AO57"/>
     <mergeCell ref="X25:AD25"/>
     <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="E51:I51"/>
     <mergeCell ref="BK31:BQ31"/>
     <mergeCell ref="AG18:AI18"/>
     <mergeCell ref="BE17:BG17"/>
+    <mergeCell ref="B55:D55"/>
     <mergeCell ref="BB21:BD21"/>
     <mergeCell ref="N6:P6"/>
     <mergeCell ref="AM25:AO25"/>
@@ -15282,15 +16175,17 @@
     <mergeCell ref="AM28:AO28"/>
     <mergeCell ref="BB18:BD18"/>
     <mergeCell ref="AG31:AI31"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="AV56:AX56"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE19 AE21:AE26 AE28:AE34 AE36:AE41 AE43:AE49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE19 AE21:AE26 AE28:AE34 AE36:AE41 AE43:AE49 AE51:AE57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG19 AG21:AG26 AG28:AG34 AG36:AG41 AG43:AG49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG19 AG21:AG26 AG28:AG34 AG36:AG41 AG43:AG49 AG51:AG57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV19 AV21:AV26 AV28:AV34 AV36:AV41 AV43:AV49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV19 AV21:AV26 AV28:AV34 AV36:AV41 AV43:AV49 AV51:AV57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
